--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_23-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_23-01-2026.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>£9.70</t>
+          <t>£10.57</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>£11.09</t>
+          <t>£12.09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -742,44 +742,44 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>£15.27</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>£18.03</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>£14.44</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>£14.59</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>£14.01</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>£18.03</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>£14.44</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>£14.59</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>£14.01</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>£14.0</t>
@@ -787,7 +787,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>£13.87</t>
+          <t>£13.81</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£14.55</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>£14.55</t>
+          <t>£15.86</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>£18.15</t>
+          <t>£19.78</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£20.24</t>
+          <t>£22.06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>£20.30</t>
+          <t>£22.13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>£23.38</t>
+          <t>£25.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>£25.40</t>
+          <t>£27.69</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>£25.00</t>
+          <t>£27.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£30.40</t>
+          <t>£33.14</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>£37.40</t>
+          <t>£40.77</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>£37.39</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>£37.79</t>
+          <t>£41.19</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£37.32</t>
+          <t>£40.68</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>£690.66</t>
+          <t>£752.82</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>£867.05</t>
+          <t>£945.08</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>£25.50</t>
+          <t>£28.56</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>£31.05</t>
+          <t>£34.78</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>£34.10</t>
+          <t>£38.19</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2383,67 +2383,67 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>£47.75</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>£40.59</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>£43.46</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>£53.63</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>£55.49</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>£68.87</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>£40.40</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
           <t>£40.45</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>£47.75</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>£40.59</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>£38.80</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>£53.63</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>£55.49</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>£68.87</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>£40.40</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>£40.45</t>
-        </is>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>£39.18</t>
+          <t>£40.80</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>£43.55</t>
+          <t>£47.47</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>£47.03</t>
+          <t>£51.26</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>£43.05</t>
+          <t>£46.92</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>£1,110.00</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>£1107.2</t>
+          <t>£1206.88</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>£1242.08</t>
+          <t>£1353.92</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>£1177.28</t>
+          <t>£1283.2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
